--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,11 +444,6 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Grupo</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
           <t>GrupoAsignado</t>
         </is>
       </c>
@@ -456,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Helmuth Andrey Baron Caceres</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11204332</v>
+        <v>79822166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -477,11 +472,6 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
           <t>Grupo 1</t>
         </is>
       </c>
@@ -489,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Helmuth Andrey Baron Caceres</t>
+          <t>Jimmy Alexander Daza Tarquino</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79822166</v>
+        <v>80208472</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -510,11 +500,6 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
           <t>Grupo 1</t>
         </is>
       </c>
@@ -522,19 +507,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Elias Alberto Santamaria Olachica</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80251217</v>
+        <v>1018432981</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4028000</v>
+        <v>2968000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -544,30 +529,25 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Grupo 1</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Adriana Milena Perez Betancourth</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>33819510</v>
+        <v>94446125</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4028000</v>
+        <v>2968000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -577,30 +557,25 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Grupo 1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jimmy Alexander Daza Tarquino</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80208472</v>
+        <v>1016066574</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4028000</v>
+        <v>2968000</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -609,31 +584,26 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Grupo 3</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Gloria Rocio Martinez</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>39724105</v>
+        <v>1022370155</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4028000</v>
+        <v>2968000</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -642,31 +612,26 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Grupo 3</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Angelica Morales Garcia</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>35379078</v>
+        <v>1030592271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>4028000</v>
+        <v>2968000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -675,31 +640,26 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Grupo 4</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jorge Medina Espinosa</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80213057</v>
+        <v>1014192228</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4028000</v>
+        <v>2968000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -708,29 +668,26 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Grupo 4</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AA22</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
+          <t>Carlos Arturo Forero Vega</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>80912134</v>
+      </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1751000</v>
+        <v>2968000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -739,29 +696,26 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grupo C</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Abordaje G1</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AA05</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>Millie Johanna Carrillo Prieto</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1031142560</v>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1751000</v>
+        <v>2544000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -770,29 +724,26 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grupo A</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Abordaje G1</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AA19</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>Jhon Fredys Moreno Maturana</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1078180826</v>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1751000</v>
+        <v>2544000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -801,29 +752,26 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grupo A</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Abordaje G1</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AA07</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>Lina Andrea Peralta Navarro</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1072719991</v>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1751000</v>
+        <v>2544000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -832,29 +780,26 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grupo D</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Abordaje G1</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AA12</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
+          <t>Gloria Rocio Martinez</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>39724105</v>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1751000</v>
+        <v>4028000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -863,29 +808,26 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grupo D</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Abordaje G1</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AA23</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
+          <t>Angelica Morales Garcia</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>35379078</v>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1751000</v>
+        <v>4028000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -894,29 +836,26 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grupo B</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Abordaje G2</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AA01</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
+          <t>Francisco Javier Plazas Gonzalez</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1014232367</v>
+      </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1751000</v>
+        <v>2968000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -925,29 +864,26 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grupo B</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Abordaje G2</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AA17</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>Excehomo Jose Morales Bernal</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>93138251</v>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1751000</v>
+        <v>2968000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -956,29 +892,26 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grupo D</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Abordaje G2</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AA03</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>Christian Felipe Martinez Camargo</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1013614915</v>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1751000</v>
+        <v>2968000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -987,29 +920,26 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grupo E</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Abordaje G2</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AA11</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
+          <t>Wendy Carolina Quintero Alvarado</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1020792634</v>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1751000</v>
+        <v>2968000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1018,29 +948,26 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grupo E</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Abordaje G2</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AA10</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>Jhon Fredy Torres Rubio</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>93298014</v>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1751000</v>
+        <v>2968000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1049,29 +976,26 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grupo A</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Abordaje G3</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AA20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
+          <t>Diego Soto Hernandez</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1024512643</v>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1751000</v>
+        <v>2968000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1080,29 +1004,26 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grupo C</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Abordaje G3</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AA15</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1030578335</v>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1751000</v>
+        <v>2968000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1111,29 +1032,26 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grupo A</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Abordaje G3</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AA21</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1073234269</v>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1751000</v>
+        <v>2544000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1142,29 +1060,26 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grupo C</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Abordaje G3</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AA04</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1030635367</v>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1751000</v>
+        <v>2544000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1173,29 +1088,26 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grupo D</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Abordaje G3</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AA14</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>Andres Guillermo Castro Coronado</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1129568417</v>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1751000</v>
+        <v>2544000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1204,29 +1116,26 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grupo C</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Abordaje G4</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AA25</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>Adriana Milena Perez Betancourth</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>33819510</v>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1751000</v>
+        <v>4028000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1235,29 +1144,26 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grupo B</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Abordaje G4</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AA02</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>Elias Alberto Santamaria Olachica</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>80251217</v>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1751000</v>
+        <v>4028000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1266,29 +1172,26 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grupo E</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Abordaje G4</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AA06</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>Alis Yuranni Garcia Ospina</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1012466465</v>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1751000</v>
+        <v>2968000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1297,29 +1200,26 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grupo A</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Abordaje G4</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AA16</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>Johan Steeven Corredor Dominguez</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1010044018</v>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1751000</v>
+        <v>2968000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1328,29 +1228,26 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grupo E</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Abordaje G4</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AA13</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>Natalia Ospina Serrato</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1013630135</v>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1751000</v>
+        <v>2968000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1359,29 +1256,26 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grupo D</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Abordaje G5</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AA08</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>Jennifer Lizcano Correa</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1000272392</v>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1751000</v>
+        <v>2968000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1390,29 +1284,26 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grupo B</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Abordaje G5</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AA09</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>Luis Fernando Rey BriceÃ±o</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1019131043</v>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1751000</v>
+        <v>2968000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1421,29 +1312,26 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grupo C</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Abordaje G5</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AA18</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>Jose Giovanny Trujillo Florez</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>80830605</v>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1751000</v>
+        <v>2968000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1452,41 +1340,1103 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grupo B</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Abordaje G5</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Solbey Yorely Alza Correa</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1024534468</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Tecnico A</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2968000</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Miguel Angel Palacio Rodriguez</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1073721158</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Tecnico B</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>2544000</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Yuli Alejandra Casas Jerez</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1032416590</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Tecnico B</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2544000</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Yerly Johana Sanchez Velasco</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1097332216</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Tecnico B</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2544000</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Grupo 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Jorge Medina Espinosa</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>80213057</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>4028000</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Jesus Eduardo Urrego Cagua</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>11204332</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Master</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4028000</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Katherine Mosquera Torres</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1024593756</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Tecnico A</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>2968000</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Viviana Andrea Chavez Enciso</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1014238905</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Tecnico A</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>2968000</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Mayerly Pardo Torres</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1012406573</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Tecnico A</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2968000</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Antonio Jose Navarrete Calderon</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1016039845</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Tecnico A</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2968000</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Lyda Astrid Recio Duarte</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1022971025</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Tecnico A</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2968000</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1018434197</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Tecnico A</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2968000</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Karen Dayana Parra Borja</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1014248976</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Tecnico A</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2968000</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Rhayza Morella Fagundez Real</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1127621316</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Tecnico B</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2544000</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Julian David Porras Sanchez</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1054681147</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tecnico B</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2544000</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Carol Chayanne Guzman Rojas</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1073687003</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Tecnico B</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2544000</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Grupo 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AA04</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Abordaje G1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>AA24</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr">
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
         <is>
           <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="D51" t="n">
         <v>1751000</v>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Grupo E</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Abordaje G1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AA20</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Abordaje G1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>AA03</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Abordaje G1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>AA08</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Abordaje G1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>AA12</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Abordaje G2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>AA11</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Abordaje G2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>AA21</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Abordaje G2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>AA06</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Abordaje G2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>AA19</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Abordaje G2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>AA15</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Abordaje G3</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>AA10</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Abordaje G3</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>AA16</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Abordaje G3</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>AA09</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Abordaje G3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>AA18</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Abordaje G3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>AA13</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Abordaje G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>AA23</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Abordaje G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AA05</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Abordaje G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>AA25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Abordaje G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AA01</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Abordaje G4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>AA22</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Abordaje G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AA07</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Abordaje G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>AA02</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Abordaje G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>AA17</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Abordaje G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>AA14</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>Abordaje G5</t>
         </is>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Helmuth Andrey Baron Caceres</t>
+          <t>Angelica Morales Garcia</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79822166</v>
+        <v>35379078</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jimmy Alexander Daza Tarquino</t>
+          <t>Jesus Eduardo Urrego Cagua</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80208472</v>
+        <v>11204332</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -507,11 +507,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1018432981</v>
+        <v>94446125</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>94446125</v>
+        <v>1030592271</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1016066574</v>
+        <v>1012466465</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1022370155</v>
+        <v>1024593756</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1030592271</v>
+        <v>80912134</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1014192228</v>
+        <v>1016066574</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>80912134</v>
+        <v>1018432981</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,11 +703,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1031142560</v>
+        <v>1078180826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1078180826</v>
+        <v>1097332216</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lina Andrea Peralta Navarro</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1072719991</v>
+        <v>1073721158</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gloria Rocio Martinez</t>
+          <t>Adriana Milena Perez Betancourth</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>39724105</v>
+        <v>33819510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -815,11 +815,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Angelica Morales Garcia</t>
+          <t>Elias Alberto Santamaria Olachica</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35379078</v>
+        <v>80251217</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1014232367</v>
+        <v>1019131043</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>93138251</v>
+        <v>1024512643</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1020792634</v>
+        <v>1000272392</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>93298014</v>
+        <v>1014192228</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1024512643</v>
+        <v>1013630135</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1030578335</v>
+        <v>1014232367</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Rhayza Morella Fagundez Real</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1030635367</v>
+        <v>1127621316</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1129568417</v>
+        <v>1030635367</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Adriana Milena Perez Betancourth</t>
+          <t>Gloria Rocio Martinez</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>33819510</v>
+        <v>39724105</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Elias Alberto Santamaria Olachica</t>
+          <t>Helmuth Andrey Baron Caceres</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>80251217</v>
+        <v>79822166</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1012466465</v>
+        <v>93138251</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1010044018</v>
+        <v>1016039845</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1013630135</v>
+        <v>1022370155</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1000272392</v>
+        <v>80830605</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1019131043</v>
+        <v>93298014</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>80830605</v>
+        <v>1024534468</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1024534468</v>
+        <v>1010044018</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,11 +1375,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1073721158</v>
+        <v>1129568417</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1032416590</v>
+        <v>1054681147</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1097332216</v>
+        <v>1031142560</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jorge Medina Espinosa</t>
+          <t>Jimmy Alexander Daza Tarquino</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>80213057</v>
+        <v>80208472</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Jorge Medina Espinosa</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>11204332</v>
+        <v>80213057</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1024593756</v>
+        <v>1022971025</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1543,11 +1543,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1014238905</v>
+        <v>1018434197</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1016039845</v>
+        <v>1020792634</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1022971025</v>
+        <v>1030578335</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1018434197</v>
+        <v>1014238905</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1711,11 +1711,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Rhayza Morella Fagundez Real</t>
+          <t>Lina Andrea Peralta Navarro</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1127621316</v>
+        <v>1072719991</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1054681147</v>
+        <v>1032416590</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AA04</t>
+          <t>AA01</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1814,14 +1814,14 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Abordaje G1</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AA24</t>
+          <t>AA02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -1840,14 +1840,14 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Abordaje G1</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AA20</t>
+          <t>AA03</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -1866,14 +1866,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Abordaje G1</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AA03</t>
+          <t>AA04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -1892,14 +1892,14 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Abordaje G1</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AA08</t>
+          <t>AA05</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -1918,14 +1918,14 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Abordaje G1</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AA12</t>
+          <t>AA06</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -1944,14 +1944,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Abordaje G2</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AA11</t>
+          <t>AA07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -1970,14 +1970,14 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Abordaje G2</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AA21</t>
+          <t>AA08</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -1996,14 +1996,14 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Abordaje G2</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AA06</t>
+          <t>AA09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2022,14 +2022,14 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Abordaje G2</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AA19</t>
+          <t>AA10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2048,14 +2048,14 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Abordaje G2</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AA15</t>
+          <t>AA11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2074,14 +2074,14 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Abordaje G3</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AA10</t>
+          <t>AA12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2100,14 +2100,14 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Abordaje G3</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AA16</t>
+          <t>AA13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2126,14 +2126,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Abordaje G3</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AA09</t>
+          <t>AA14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2152,14 +2152,14 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Abordaje G3</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AA18</t>
+          <t>AA15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2178,14 +2178,14 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Abordaje G3</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AA13</t>
+          <t>AA16</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2204,14 +2204,14 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Abordaje G4</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AA23</t>
+          <t>AA17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2230,14 +2230,14 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Abordaje G4</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AA05</t>
+          <t>AA18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2256,14 +2256,14 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Abordaje G4</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AA25</t>
+          <t>AA19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2282,14 +2282,14 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Abordaje G4</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AA01</t>
+          <t>AA20</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2308,14 +2308,14 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Abordaje G4</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AA22</t>
+          <t>AA21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2334,14 +2334,14 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Abordaje G5</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AA07</t>
+          <t>AA22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2360,14 +2360,14 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Abordaje G5</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AA02</t>
+          <t>AA23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2386,14 +2386,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Abordaje G5</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AA17</t>
+          <t>AA24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2412,14 +2412,14 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Abordaje G5</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AA14</t>
+          <t>AA25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Abordaje G5</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Angelica Morales Garcia</t>
+          <t>Helmuth Andrey Baron Caceres</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35379078</v>
+        <v>79822166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Jimmy Alexander Daza Tarquino</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11204332</v>
+        <v>80208472</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -507,11 +507,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>94446125</v>
+        <v>1030592271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1030592271</v>
+        <v>94446125</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1012466465</v>
+        <v>93138251</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1024593756</v>
+        <v>1000272392</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>80912134</v>
+        <v>1013630135</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1016066574</v>
+        <v>93298014</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1018432981</v>
+        <v>1014192228</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,11 +703,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1078180826</v>
+        <v>1032416590</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
+          <t>Lina Andrea Peralta Navarro</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1097332216</v>
+        <v>1072719991</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1073721158</v>
+        <v>1073234269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Adriana Milena Perez Betancourth</t>
+          <t>Jorge Medina Espinosa</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33819510</v>
+        <v>80213057</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -815,11 +815,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Elias Alberto Santamaria Olachica</t>
+          <t>Gloria Rocio Martinez</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>80251217</v>
+        <v>39724105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1019131043</v>
+        <v>1014238905</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1024512643</v>
+        <v>1022971025</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1013614915</v>
+        <v>1019131043</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1000272392</v>
+        <v>1022370155</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1014192228</v>
+        <v>80830605</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1013630135</v>
+        <v>1024593756</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1014232367</v>
+        <v>1016066574</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1039,11 +1039,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1073234269</v>
+        <v>1031142560</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rhayza Morella Fagundez Real</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1127621316</v>
+        <v>1073721158</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1030635367</v>
+        <v>1073687003</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Gloria Rocio Martinez</t>
+          <t>Angelica Morales Garcia</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>39724105</v>
+        <v>35379078</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Helmuth Andrey Baron Caceres</t>
+          <t>Adriana Milena Perez Betancourth</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>79822166</v>
+        <v>33819510</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>93138251</v>
+        <v>1012406573</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1016039845</v>
+        <v>1012466465</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1022370155</v>
+        <v>1010044018</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>80830605</v>
+        <v>1018434197</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>93298014</v>
+        <v>1014232367</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1024534468</v>
+        <v>1014248976</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1010044018</v>
+        <v>1013614915</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,11 +1375,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1129568417</v>
+        <v>1054681147</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1054681147</v>
+        <v>1030635367</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1031142560</v>
+        <v>1078180826</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jimmy Alexander Daza Tarquino</t>
+          <t>Jesus Eduardo Urrego Cagua</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>80208472</v>
+        <v>11204332</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jorge Medina Espinosa</t>
+          <t>Elias Alberto Santamaria Olachica</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>80213057</v>
+        <v>80251217</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1022971025</v>
+        <v>1030578335</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1543,11 +1543,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1018434197</v>
+        <v>1024512643</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1012406573</v>
+        <v>80912134</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1020792634</v>
+        <v>1018432981</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1030578335</v>
+        <v>1020792634</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1014238905</v>
+        <v>1024534468</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1014248976</v>
+        <v>1016039845</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1711,11 +1711,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Lina Andrea Peralta Navarro</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1072719991</v>
+        <v>1129568417</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Rhayza Morella Fagundez Real</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1032416590</v>
+        <v>1127621316</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1767,11 +1767,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1073687003</v>
+        <v>1097332216</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2437,6 +2437,58 @@
         </is>
       </c>
       <c r="F74" t="inlineStr">
+        <is>
+          <t>Abordaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>AA26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Abordaje</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>AA27</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1751000</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>Abordaje</t>
         </is>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>GrupoAsignado</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Tipo_Personal</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -475,6 +480,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -503,6 +513,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -531,6 +546,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -559,6 +579,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -587,6 +612,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -615,6 +645,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -643,6 +678,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -671,6 +711,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -699,6 +744,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -727,6 +777,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -755,6 +810,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -783,6 +843,11 @@
           <t>Grupo 1</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -811,6 +876,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -839,6 +909,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,6 +942,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -895,6 +975,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -923,6 +1008,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -951,6 +1041,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -979,6 +1074,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1007,6 +1107,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1035,6 +1140,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1063,6 +1173,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1091,6 +1206,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1119,6 +1239,11 @@
           <t>Grupo 2</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1147,6 +1272,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1175,6 +1305,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1203,6 +1338,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1231,6 +1371,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1259,6 +1404,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1287,6 +1437,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1315,6 +1470,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1343,6 +1503,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1371,6 +1536,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1399,6 +1569,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1427,6 +1602,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1455,6 +1635,11 @@
           <t>Grupo 3</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1483,6 +1668,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1511,6 +1701,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1539,6 +1734,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1567,6 +1767,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1595,6 +1800,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1623,6 +1833,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1651,6 +1866,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1679,6 +1899,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1707,6 +1932,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1735,6 +1965,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1763,6 +1998,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1791,6 +2031,11 @@
           <t>Grupo 4</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1817,6 +2062,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1843,6 +2093,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1869,6 +2124,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1895,6 +2155,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1921,6 +2186,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1947,6 +2217,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1973,6 +2248,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1999,6 +2279,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2025,6 +2310,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2051,6 +2341,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2077,6 +2372,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2103,6 +2403,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2129,6 +2434,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2155,6 +2465,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2181,6 +2496,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2207,6 +2527,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2233,6 +2558,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2259,6 +2589,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2285,6 +2620,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2311,6 +2651,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2337,6 +2682,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2363,6 +2713,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2389,6 +2744,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2415,6 +2775,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2441,6 +2806,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2467,6 +2837,11 @@
           <t>Abordaje</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2491,6 +2866,11 @@
       <c r="F76" t="inlineStr">
         <is>
           <t>Abordaje</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Técnicos</t>
         </is>
       </c>
     </row>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,20 +447,15 @@
           <t>GrupoAsignado</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Tipo_Personal</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Helmuth Andrey Baron Caceres</t>
+          <t>Adriana Milena Perez Betancourth</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>79822166</v>
+        <v>33819510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -480,20 +475,15 @@
           <t>Grupo 1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jimmy Alexander Daza Tarquino</t>
+          <t>Jesus Eduardo Urrego Cagua</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80208472</v>
+        <v>11204332</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -513,20 +503,15 @@
           <t>Grupo 1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1030592271</v>
+        <v>80830605</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -544,22 +529,17 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>Grupo 1</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>94446125</v>
+        <v>1010044018</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -577,22 +557,17 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Grupo 1</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93138251</v>
+        <v>1016039845</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -610,22 +585,17 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Grupo 1</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1000272392</v>
+        <v>1030578335</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -643,22 +613,17 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Grupo 1</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1013630135</v>
+        <v>1000272392</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -676,22 +641,17 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>Grupo 1</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93298014</v>
+        <v>1020792634</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -709,22 +669,17 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Grupo 1</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1014192228</v>
+        <v>1014248976</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -742,22 +697,17 @@
       <c r="F10" t="inlineStr">
         <is>
           <t>Grupo 1</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1032416590</v>
+        <v>1073234269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -777,20 +727,15 @@
           <t>Grupo 1</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lina Andrea Peralta Navarro</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1072719991</v>
+        <v>1054681147</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -810,20 +755,15 @@
           <t>Grupo 1</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Lina Andrea Peralta Navarro</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1073234269</v>
+        <v>1072719991</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -843,20 +783,15 @@
           <t>Grupo 1</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Jorge Medina Espinosa</t>
+          <t>Gloria Rocio Martinez</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80213057</v>
+        <v>39724105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -876,20 +811,15 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Gloria Rocio Martinez</t>
+          <t>Jorge Medina Espinosa</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>39724105</v>
+        <v>80213057</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -909,20 +839,15 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1014238905</v>
+        <v>1013614915</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -940,22 +865,17 @@
       <c r="F16" t="inlineStr">
         <is>
           <t>Grupo 2</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1022971025</v>
+        <v>1019131043</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -973,22 +893,17 @@
       <c r="F17" t="inlineStr">
         <is>
           <t>Grupo 2</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1019131043</v>
+        <v>94446125</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1006,22 +921,17 @@
       <c r="F18" t="inlineStr">
         <is>
           <t>Grupo 2</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1022370155</v>
+        <v>80912134</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1039,22 +949,17 @@
       <c r="F19" t="inlineStr">
         <is>
           <t>Grupo 2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>80830605</v>
+        <v>1014238905</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1072,22 +977,17 @@
       <c r="F20" t="inlineStr">
         <is>
           <t>Grupo 2</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1024593756</v>
+        <v>1012406573</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1105,22 +1005,17 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Grupo 2</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1016066574</v>
+        <v>1012466465</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1138,22 +1033,17 @@
       <c r="F22" t="inlineStr">
         <is>
           <t>Grupo 2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1031142560</v>
+        <v>1032416590</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1173,20 +1063,15 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1073721158</v>
+        <v>1129568417</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1206,20 +1091,15 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1073687003</v>
+        <v>1030635367</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1239,11 +1119,6 @@
           <t>Grupo 2</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1272,20 +1147,15 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Adriana Milena Perez Betancourth</t>
+          <t>Elias Alberto Santamaria Olachica</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>33819510</v>
+        <v>80251217</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1305,20 +1175,15 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1012406573</v>
+        <v>93138251</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1336,22 +1201,17 @@
       <c r="F28" t="inlineStr">
         <is>
           <t>Grupo 3</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1012466465</v>
+        <v>1016066574</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1369,22 +1229,17 @@
       <c r="F29" t="inlineStr">
         <is>
           <t>Grupo 3</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1010044018</v>
+        <v>93298014</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1402,22 +1257,17 @@
       <c r="F30" t="inlineStr">
         <is>
           <t>Grupo 3</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1018434197</v>
+        <v>1022971025</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1435,11 +1285,6 @@
       <c r="F31" t="inlineStr">
         <is>
           <t>Grupo 3</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
@@ -1470,20 +1315,15 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1014248976</v>
+        <v>1022370155</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1501,22 +1341,17 @@
       <c r="F33" t="inlineStr">
         <is>
           <t>Grupo 3</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1013614915</v>
+        <v>1013630135</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1534,22 +1369,17 @@
       <c r="F34" t="inlineStr">
         <is>
           <t>Grupo 3</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1054681147</v>
+        <v>1031142560</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1569,20 +1399,15 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Rhayza Morella Fagundez Real</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1030635367</v>
+        <v>1127621316</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1602,20 +1427,15 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1078180826</v>
+        <v>1073721158</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1635,20 +1455,15 @@
           <t>Grupo 3</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Jimmy Alexander Daza Tarquino</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>11204332</v>
+        <v>80208472</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1668,20 +1483,15 @@
           <t>Grupo 4</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Elias Alberto Santamaria Olachica</t>
+          <t>Helmuth Andrey Baron Caceres</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>80251217</v>
+        <v>79822166</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1701,20 +1511,15 @@
           <t>Grupo 4</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1030578335</v>
+        <v>1024534468</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1732,22 +1537,17 @@
       <c r="F40" t="inlineStr">
         <is>
           <t>Grupo 4</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1024512643</v>
+        <v>1014192228</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1765,22 +1565,17 @@
       <c r="F41" t="inlineStr">
         <is>
           <t>Grupo 4</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>80912134</v>
+        <v>1024512643</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1798,11 +1593,6 @@
       <c r="F42" t="inlineStr">
         <is>
           <t>Grupo 4</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
@@ -1833,20 +1623,15 @@
           <t>Grupo 4</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1020792634</v>
+        <v>1024593756</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1864,22 +1649,17 @@
       <c r="F44" t="inlineStr">
         <is>
           <t>Grupo 4</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1024534468</v>
+        <v>1030592271</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1897,22 +1677,17 @@
       <c r="F45" t="inlineStr">
         <is>
           <t>Grupo 4</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1016039845</v>
+        <v>1018434197</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1930,22 +1705,17 @@
       <c r="F46" t="inlineStr">
         <is>
           <t>Grupo 4</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1129568417</v>
+        <v>1078180826</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1965,20 +1735,15 @@
           <t>Grupo 4</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Rhayza Morella Fagundez Real</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1127621316</v>
+        <v>1073687003</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1998,11 +1763,6 @@
           <t>Grupo 4</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2031,11 +1791,6 @@
           <t>Grupo 4</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2062,11 +1817,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2093,11 +1843,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2124,11 +1869,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2155,11 +1895,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2186,11 +1921,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2217,11 +1947,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2248,11 +1973,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2279,11 +1999,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2310,11 +2025,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2341,11 +2051,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2372,11 +2077,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2403,11 +2103,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2434,11 +2129,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2465,11 +2155,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2496,11 +2181,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2527,11 +2207,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2558,11 +2233,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2589,11 +2259,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2620,11 +2285,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2651,11 +2311,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2682,11 +2337,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2713,11 +2363,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2744,11 +2389,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2775,11 +2415,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2806,11 +2441,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2837,11 +2467,6 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2868,11 +2493,102 @@
           <t>Abordaje</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Técnicos</t>
-        </is>
-      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Supervisor 1</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1111111</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Supervisor 2</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>2222222</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Supervisor 3</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>3333333</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Supervisor 4</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>444444</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Supervisor</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Cablemovil</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -451,19 +451,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Adriana Milena Perez Betancourth</t>
+          <t>Supervisor 2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33819510</v>
+        <v>2222222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Supervisor</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4028000</v>
+        <v>5000000</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Adriana Milena Perez Betancourth</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11204332</v>
+        <v>33819510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -507,19 +507,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Jesus Eduardo Urrego Cagua</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80830605</v>
+        <v>11204332</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2968000</v>
+        <v>4028000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1010044018</v>
+        <v>1024534468</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1016039845</v>
+        <v>1013614915</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1030578335</v>
+        <v>1016066574</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1000272392</v>
+        <v>94446125</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1020792634</v>
+        <v>1012466465</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1014248976</v>
+        <v>1019131043</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,19 +703,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1073234269</v>
+        <v>1022370155</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2544000</v>
+        <v>2968000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1054681147</v>
+        <v>1031142560</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -787,19 +787,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Gloria Rocio Martinez</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>39724105</v>
+        <v>1097332216</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4028000</v>
+        <v>2544000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -808,26 +808,26 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jorge Medina Espinosa</t>
+          <t>Supervisor 1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>80213057</v>
+        <v>1111111</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Supervisor</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4028000</v>
+        <v>5000000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -843,19 +843,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Elias Alberto Santamaria Olachica</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1013614915</v>
+        <v>80251217</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2968000</v>
+        <v>4028000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -871,19 +871,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Jimmy Alexander Daza Tarquino</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1019131043</v>
+        <v>80208472</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2968000</v>
+        <v>4028000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>94446125</v>
+        <v>1014248976</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>80912134</v>
+        <v>1014238905</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1014238905</v>
+        <v>1013630135</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1012406573</v>
+        <v>93138251</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1012466465</v>
+        <v>1000272392</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1039,19 +1039,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1032416590</v>
+        <v>1024593756</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2544000</v>
+        <v>2968000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1129568417</v>
+        <v>1018432981</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2544000</v>
+        <v>2968000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1030635367</v>
+        <v>1129568417</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Angelica Morales Garcia</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>35379078</v>
+        <v>1078180826</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4028000</v>
+        <v>2544000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1144,26 +1144,26 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Elias Alberto Santamaria Olachica</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>80251217</v>
+        <v>1073234269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4028000</v>
+        <v>2544000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1172,26 +1172,26 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Supervisor 3</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>93138251</v>
+        <v>3333333</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Supervisor</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2968000</v>
+        <v>5000000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1207,19 +1207,19 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Helmuth Andrey Baron Caceres</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1016066574</v>
+        <v>79822166</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2968000</v>
+        <v>4028000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1235,19 +1235,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Angelica Morales Garcia</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>93298014</v>
+        <v>35379078</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2968000</v>
+        <v>4028000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1022971025</v>
+        <v>1016039845</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1014232367</v>
+        <v>1014192228</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1022370155</v>
+        <v>1030578335</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1013630135</v>
+        <v>1030592271</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,19 +1375,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1031142560</v>
+        <v>1012406573</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2544000</v>
+        <v>2968000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1403,19 +1403,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rhayza Morella Fagundez Real</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1127621316</v>
+        <v>1020792634</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2544000</v>
+        <v>2968000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1431,19 +1431,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1073721158</v>
+        <v>1022971025</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2544000</v>
+        <v>2968000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jimmy Alexander Daza Tarquino</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>80208472</v>
+        <v>1073721158</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4028000</v>
+        <v>2544000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1480,26 +1480,26 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Helmuth Andrey Baron Caceres</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>79822166</v>
+        <v>1073687003</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4028000</v>
+        <v>2544000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1508,26 +1508,26 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Rhayza Morella Fagundez Real</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1024534468</v>
+        <v>1127621316</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2968000</v>
+        <v>2544000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1536,26 +1536,26 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Supervisor 4</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1014192228</v>
+        <v>444444</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Supervisor</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2968000</v>
+        <v>5000000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1571,19 +1571,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Gloria Rocio Martinez</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1024512643</v>
+        <v>39724105</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2968000</v>
+        <v>4028000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1599,19 +1599,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Jorge Medina Espinosa</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1018432981</v>
+        <v>80213057</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2968000</v>
+        <v>4028000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1024593756</v>
+        <v>80912134</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1030592271</v>
+        <v>1010044018</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1018434197</v>
+        <v>80830605</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1711,19 +1711,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1078180826</v>
+        <v>1018434197</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2544000</v>
+        <v>2968000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1739,19 +1739,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1073687003</v>
+        <v>93298014</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2544000</v>
+        <v>2968000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1767,19 +1767,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1097332216</v>
+        <v>1024512643</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2544000</v>
+        <v>2968000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1795,17 +1795,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AA01</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>Francisco Javier Plazas Gonzalez</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1014232367</v>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1751000</v>
+        <v>2968000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1814,24 +1816,26 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Abordaje</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AA02</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>Julian David Porras Sanchez</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1054681147</v>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1751000</v>
+        <v>2544000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1840,24 +1844,26 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Abordaje</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AA03</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr"/>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1030635367</v>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1751000</v>
+        <v>2544000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1866,24 +1872,26 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Abordaje</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AA04</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr"/>
+          <t>Yuli Alejandra Casas Jerez</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1032416590</v>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1751000</v>
+        <v>2544000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1892,14 +1900,14 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Abordaje</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AA05</t>
+          <t>AA01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -1925,7 +1933,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AA06</t>
+          <t>AA02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -1951,7 +1959,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AA07</t>
+          <t>AA03</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -1977,7 +1985,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AA08</t>
+          <t>AA04</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2003,7 +2011,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AA09</t>
+          <t>AA05</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2029,7 +2037,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AA10</t>
+          <t>AA06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2055,7 +2063,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AA11</t>
+          <t>AA07</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2081,7 +2089,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AA12</t>
+          <t>AA08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2107,7 +2115,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AA13</t>
+          <t>AA09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2133,7 +2141,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AA14</t>
+          <t>AA10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2159,7 +2167,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AA15</t>
+          <t>AA11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2185,7 +2193,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AA16</t>
+          <t>AA12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2211,7 +2219,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AA17</t>
+          <t>AA13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2237,7 +2245,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AA18</t>
+          <t>AA14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2263,7 +2271,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AA19</t>
+          <t>AA15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2289,7 +2297,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AA20</t>
+          <t>AA16</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2315,7 +2323,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AA21</t>
+          <t>AA17</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2341,7 +2349,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AA22</t>
+          <t>AA18</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2367,7 +2375,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AA23</t>
+          <t>AA19</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2393,7 +2401,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AA24</t>
+          <t>AA20</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2419,7 +2427,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AA25</t>
+          <t>AA21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -2445,7 +2453,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AA26</t>
+          <t>AA22</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2471,7 +2479,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AA27</t>
+          <t>AA23</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -2497,98 +2505,106 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Supervisor 1</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>1111111</v>
-      </c>
+          <t>AA24</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Supervisor</t>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>5000000</v>
+        <v>1751000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>Cablemovil</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Abordaje</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Supervisor 2</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>2222222</v>
-      </c>
+          <t>AA25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Supervisor</t>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5000000</v>
+        <v>1751000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>Cablemovil</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Abordaje</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Supervisor 3</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>3333333</v>
-      </c>
+          <t>AA26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Supervisor</t>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5000000</v>
+        <v>1751000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>Cablemovil</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Abordaje</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Supervisor 4</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>444444</v>
-      </c>
+          <t>AA27</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Supervisor</t>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>5000000</v>
+        <v>1751000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>Cablemovil</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Abordaje</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Supervisor 2</t>
+          <t>Supervisor 4</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2222222</v>
+        <v>444444</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Adriana Milena Perez Betancourth</t>
+          <t>Jorge Medina Espinosa</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33819510</v>
+        <v>80213057</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -507,11 +507,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Angelica Morales Garcia</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11204332</v>
+        <v>35379078</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1024534468</v>
+        <v>1024593756</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1013614915</v>
+        <v>1016066574</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1016066574</v>
+        <v>1030592271</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>94446125</v>
+        <v>1016039845</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1012466465</v>
+        <v>1000272392</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1019131043</v>
+        <v>1030578335</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,11 +703,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1022370155</v>
+        <v>1010044018</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1031142560</v>
+        <v>1073234269</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lina Andrea Peralta Navarro</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1072719991</v>
+        <v>1054681147</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1097332216</v>
+        <v>1031142560</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Elias Alberto Santamaria Olachica</t>
+          <t>Adriana Milena Perez Betancourth</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>80251217</v>
+        <v>33819510</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jimmy Alexander Daza Tarquino</t>
+          <t>Jesus Eduardo Urrego Cagua</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>80208472</v>
+        <v>11204332</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1014248976</v>
+        <v>93298014</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1014238905</v>
+        <v>93138251</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1013630135</v>
+        <v>1018432981</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>93138251</v>
+        <v>1014232367</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1000272392</v>
+        <v>1018434197</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1039,11 +1039,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1024593756</v>
+        <v>1019131043</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1018432981</v>
+        <v>1012406573</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1129568417</v>
+        <v>1030635367</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1078180826</v>
+        <v>1032416590</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Rhayza Morella Fagundez Real</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1073234269</v>
+        <v>1127621316</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Angelica Morales Garcia</t>
+          <t>Gloria Rocio Martinez</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>35379078</v>
+        <v>39724105</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1016039845</v>
+        <v>94446125</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1014192228</v>
+        <v>1014248976</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1030578335</v>
+        <v>1014238905</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1030592271</v>
+        <v>1013614915</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,11 +1375,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1012406573</v>
+        <v>80830605</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1020792634</v>
+        <v>1024512643</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1022971025</v>
+        <v>1024534468</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1073687003</v>
+        <v>1129568417</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rhayza Morella Fagundez Real</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1127621316</v>
+        <v>1097332216</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1543,11 +1543,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Supervisor 4</t>
+          <t>Supervisor 2</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>444444</v>
+        <v>2222222</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Gloria Rocio Martinez</t>
+          <t>Jimmy Alexander Daza Tarquino</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>39724105</v>
+        <v>80208472</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jorge Medina Espinosa</t>
+          <t>Elias Alberto Santamaria Olachica</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>80213057</v>
+        <v>80251217</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>80912134</v>
+        <v>1014192228</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1010044018</v>
+        <v>1020792634</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>80830605</v>
+        <v>1022370155</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1711,11 +1711,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1018434197</v>
+        <v>1022971025</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>93298014</v>
+        <v>80912134</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1767,11 +1767,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1024512643</v>
+        <v>1013630135</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1795,11 +1795,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1014232367</v>
+        <v>1012466465</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1823,11 +1823,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1054681147</v>
+        <v>1078180826</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1851,11 +1851,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1030635367</v>
+        <v>1073687003</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1879,11 +1879,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Lina Andrea Peralta Navarro</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1032416590</v>
+        <v>1072719991</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jorge Medina Espinosa</t>
+          <t>Gloria Rocio Martinez</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80213057</v>
+        <v>39724105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -507,11 +507,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Angelica Morales Garcia</t>
+          <t>Elias Alberto Santamaria Olachica</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>35379078</v>
+        <v>80251217</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1024593756</v>
+        <v>93298014</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1016066574</v>
+        <v>1014238905</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1030592271</v>
+        <v>1019131043</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1016039845</v>
+        <v>1018432981</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1000272392</v>
+        <v>1016039845</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1030578335</v>
+        <v>80912134</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,11 +703,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1010044018</v>
+        <v>1030578335</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1073234269</v>
+        <v>1129568417</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1054681147</v>
+        <v>1030635367</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1031142560</v>
+        <v>1032416590</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -815,11 +815,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Supervisor 1</t>
+          <t>Supervisor 3</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1111111</v>
+        <v>3333333</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Adriana Milena Perez Betancourth</t>
+          <t>Helmuth Andrey Baron Caceres</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>33819510</v>
+        <v>79822166</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Jorge Medina Espinosa</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11204332</v>
+        <v>80213057</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>93298014</v>
+        <v>1000272392</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>93138251</v>
+        <v>80830605</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1018432981</v>
+        <v>1012406573</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1014232367</v>
+        <v>1016066574</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1018434197</v>
+        <v>1013630135</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1039,11 +1039,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1019131043</v>
+        <v>94446125</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1012406573</v>
+        <v>1024512643</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Rhayza Morella Fagundez Real</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1030635367</v>
+        <v>1127621316</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1032416590</v>
+        <v>1054681147</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rhayza Morella Fagundez Real</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1127621316</v>
+        <v>1078180826</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Supervisor 3</t>
+          <t>Supervisor 2</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3333333</v>
+        <v>2222222</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Helmuth Andrey Baron Caceres</t>
+          <t>Adriana Milena Perez Betancourth</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>79822166</v>
+        <v>33819510</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gloria Rocio Martinez</t>
+          <t>Angelica Morales Garcia</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>39724105</v>
+        <v>35379078</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>94446125</v>
+        <v>1014248976</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1014248976</v>
+        <v>1012466465</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1014238905</v>
+        <v>1014192228</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1013614915</v>
+        <v>1022370155</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,11 +1375,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>80830605</v>
+        <v>1020792634</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1024512643</v>
+        <v>1010044018</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1024534468</v>
+        <v>1013614915</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1073721158</v>
+        <v>1073687003</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1129568417</v>
+        <v>1031142560</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1543,11 +1543,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Supervisor 2</t>
+          <t>Supervisor 1</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2222222</v>
+        <v>1111111</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jimmy Alexander Daza Tarquino</t>
+          <t>Jesus Eduardo Urrego Cagua</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>80208472</v>
+        <v>11204332</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Elias Alberto Santamaria Olachica</t>
+          <t>Jimmy Alexander Daza Tarquino</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>80251217</v>
+        <v>80208472</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1014192228</v>
+        <v>1024534468</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1020792634</v>
+        <v>1014232367</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1022370155</v>
+        <v>1024593756</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1711,11 +1711,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1022971025</v>
+        <v>1030592271</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>80912134</v>
+        <v>1018434197</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1767,11 +1767,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1013630135</v>
+        <v>1022971025</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1795,11 +1795,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1012466465</v>
+        <v>93138251</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1823,11 +1823,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Lina Andrea Peralta Navarro</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1078180826</v>
+        <v>1072719991</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1851,11 +1851,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1073687003</v>
+        <v>1073721158</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1879,11 +1879,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Lina Andrea Peralta Navarro</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1072719991</v>
+        <v>1073234269</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Supervisor 4</t>
+          <t>Supervisor 2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>444444</v>
+        <v>2222222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gloria Rocio Martinez</t>
+          <t>Jesus Eduardo Urrego Cagua</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39724105</v>
+        <v>11204332</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>93298014</v>
+        <v>1012466465</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1014238905</v>
+        <v>1022370155</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1019131043</v>
+        <v>1013614915</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1018432981</v>
+        <v>94446125</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1016039845</v>
+        <v>93298014</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>80912134</v>
+        <v>1030592271</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,11 +703,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1030578335</v>
+        <v>1024534468</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1129568417</v>
+        <v>1078180826</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1030635367</v>
+        <v>1054681147</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Rhayza Morella Fagundez Real</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1032416590</v>
+        <v>1127621316</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -815,11 +815,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Supervisor 3</t>
+          <t>Supervisor 4</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3333333</v>
+        <v>444444</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Helmuth Andrey Baron Caceres</t>
+          <t>Jimmy Alexander Daza Tarquino</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>79822166</v>
+        <v>80208472</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jorge Medina Espinosa</t>
+          <t>Angelica Morales Garcia</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>80213057</v>
+        <v>35379078</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1000272392</v>
+        <v>1014238905</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>80830605</v>
+        <v>1019131043</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1012406573</v>
+        <v>1022971025</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1016066574</v>
+        <v>1014248976</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1013630135</v>
+        <v>1000272392</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1039,11 +1039,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>94446125</v>
+        <v>80912134</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1024512643</v>
+        <v>1016039845</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rhayza Morella Fagundez Real</t>
+          <t>Lina Andrea Peralta Navarro</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1127621316</v>
+        <v>1072719991</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1054681147</v>
+        <v>1129568417</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1078180826</v>
+        <v>1097332216</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Supervisor 2</t>
+          <t>Supervisor 1</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2222222</v>
+        <v>1111111</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Adriana Milena Perez Betancourth</t>
+          <t>Gloria Rocio Martinez</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>33819510</v>
+        <v>39724105</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Angelica Morales Garcia</t>
+          <t>Helmuth Andrey Baron Caceres</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>35379078</v>
+        <v>79822166</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1014248976</v>
+        <v>1014192228</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1012466465</v>
+        <v>1018434197</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1014192228</v>
+        <v>1013630135</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1022370155</v>
+        <v>1024593756</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,11 +1375,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1020792634</v>
+        <v>1016066574</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1010044018</v>
+        <v>1018432981</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1013614915</v>
+        <v>93138251</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1073687003</v>
+        <v>1073721158</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1097332216</v>
+        <v>1073687003</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1543,11 +1543,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Supervisor 1</t>
+          <t>Supervisor 3</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1111111</v>
+        <v>3333333</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Jorge Medina Espinosa</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>11204332</v>
+        <v>80213057</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jimmy Alexander Daza Tarquino</t>
+          <t>Adriana Milena Perez Betancourth</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>80208472</v>
+        <v>33819510</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1024534468</v>
+        <v>1030578335</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1014232367</v>
+        <v>1020792634</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1024593756</v>
+        <v>1010044018</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1711,11 +1711,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1030592271</v>
+        <v>1014232367</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1018434197</v>
+        <v>80830605</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1767,11 +1767,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1022971025</v>
+        <v>1024512643</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1795,11 +1795,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>93138251</v>
+        <v>1012406573</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1823,11 +1823,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Lina Andrea Peralta Navarro</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1072719991</v>
+        <v>1073234269</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1851,11 +1851,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1073721158</v>
+        <v>1030635367</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1879,11 +1879,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1073234269</v>
+        <v>1032416590</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Supervisor 2</t>
+          <t>Supervisor 4</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2222222</v>
+        <v>444444</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Gloria Rocio Martinez</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11204332</v>
+        <v>39724105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1012466465</v>
+        <v>93298014</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1022370155</v>
+        <v>1022971025</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1013614915</v>
+        <v>1022370155</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>94446125</v>
+        <v>1016039845</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>93298014</v>
+        <v>1024534468</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1030592271</v>
+        <v>1012466465</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,11 +703,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1024534468</v>
+        <v>93138251</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1078180826</v>
+        <v>1073687003</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1054681147</v>
+        <v>1073234269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -815,11 +815,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Supervisor 4</t>
+          <t>Supervisor 2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>444444</v>
+        <v>2222222</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Jimmy Alexander Daza Tarquino</t>
+          <t>Angelica Morales Garcia</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>80208472</v>
+        <v>35379078</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Angelica Morales Garcia</t>
+          <t>Jorge Medina Espinosa</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>35379078</v>
+        <v>80213057</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1014238905</v>
+        <v>1030592271</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1019131043</v>
+        <v>1030578335</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1022971025</v>
+        <v>1012406573</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1014248976</v>
+        <v>1018434197</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1000272392</v>
+        <v>1010044018</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1039,11 +1039,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>80912134</v>
+        <v>1024593756</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1016039845</v>
+        <v>1018432981</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lina Andrea Peralta Navarro</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1072719991</v>
+        <v>1030635367</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1129568417</v>
+        <v>1031142560</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1097332216</v>
+        <v>1073721158</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gloria Rocio Martinez</t>
+          <t>Helmuth Andrey Baron Caceres</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>39724105</v>
+        <v>79822166</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Helmuth Andrey Baron Caceres</t>
+          <t>Jesus Eduardo Urrego Cagua</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>79822166</v>
+        <v>11204332</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1014192228</v>
+        <v>1014238905</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1018434197</v>
+        <v>1013614915</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1013630135</v>
+        <v>1016066574</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1024593756</v>
+        <v>1014248976</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,11 +1375,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1016066574</v>
+        <v>1020792634</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1018432981</v>
+        <v>1000272392</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>93138251</v>
+        <v>94446125</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1073721158</v>
+        <v>1078180826</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1031142560</v>
+        <v>1032416590</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1073687003</v>
+        <v>1054681147</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jorge Medina Espinosa</t>
+          <t>Jimmy Alexander Daza Tarquino</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>80213057</v>
+        <v>80208472</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1030578335</v>
+        <v>80830605</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1020792634</v>
+        <v>1019131043</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1010044018</v>
+        <v>1014192228</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1711,11 +1711,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1014232367</v>
+        <v>1013630135</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>80830605</v>
+        <v>1014232367</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1767,11 +1767,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1024512643</v>
+        <v>80912134</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1795,11 +1795,11 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1012406573</v>
+        <v>1024512643</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1823,11 +1823,11 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Lina Andrea Peralta Navarro</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1073234269</v>
+        <v>1072719991</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1851,11 +1851,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1030635367</v>
+        <v>1097332216</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1879,11 +1879,11 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1032416590</v>
+        <v>1129568417</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Supervisor 4</t>
+          <t>Supervisor 1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>444444</v>
+        <v>1111111</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gloria Rocio Martinez</t>
+          <t>Elias Alberto Santamaria Olachica</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39724105</v>
+        <v>80251217</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -507,19 +507,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Elias Alberto Santamaria Olachica</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80251217</v>
+        <v>1030592271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4028000</v>
+        <v>2968000</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>93298014</v>
+        <v>1014232367</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1022971025</v>
+        <v>1020792634</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1022370155</v>
+        <v>1024512643</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1016039845</v>
+        <v>1013614915</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1024534468</v>
+        <v>94446125</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1012466465</v>
+        <v>1019131043</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,19 +703,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Rhayza Morella Fagundez Real</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>93138251</v>
+        <v>1127621316</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2968000</v>
+        <v>2544000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1073687003</v>
+        <v>1031142560</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1073234269</v>
+        <v>1078180826</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -787,19 +787,19 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Rhayza Morella Fagundez Real</t>
+          <t>Supervisor 4</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1127621316</v>
+        <v>444444</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t>Supervisor</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2544000</v>
+        <v>5000000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -808,26 +808,26 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grupo 1</t>
+          <t>Grupo 2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Supervisor 2</t>
+          <t>Adriana Milena Perez Betancourth</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2222222</v>
+        <v>33819510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Supervisor</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5000000</v>
+        <v>4028000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -843,19 +843,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Angelica Morales Garcia</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>35379078</v>
+        <v>80912134</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4028000</v>
+        <v>2968000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -871,19 +871,19 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jorge Medina Espinosa</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>80213057</v>
+        <v>1013630135</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4028000</v>
+        <v>2968000</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1030592271</v>
+        <v>80830605</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1030578335</v>
+        <v>1022370155</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1012406573</v>
+        <v>1014238905</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1018434197</v>
+        <v>1012406573</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1010044018</v>
+        <v>1018434197</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1039,19 +1039,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1024593756</v>
+        <v>1032416590</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2968000</v>
+        <v>2544000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1018432981</v>
+        <v>1073687003</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2968000</v>
+        <v>2544000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1123,19 +1123,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Supervisor 3</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1031142560</v>
+        <v>3333333</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t>Supervisor</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2544000</v>
+        <v>5000000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1144,26 +1144,26 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Gloria Rocio Martinez</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1073721158</v>
+        <v>39724105</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2544000</v>
+        <v>4028000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1172,26 +1172,26 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grupo 2</t>
+          <t>Grupo 3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Supervisor 1</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1111111</v>
+        <v>1010044018</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Supervisor</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5000000</v>
+        <v>2968000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1207,19 +1207,19 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Helmuth Andrey Baron Caceres</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>79822166</v>
+        <v>1022971025</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4028000</v>
+        <v>2968000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1235,19 +1235,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>11204332</v>
+        <v>93298014</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>4028000</v>
+        <v>2968000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1014238905</v>
+        <v>1014248976</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1013614915</v>
+        <v>1014192228</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1016066574</v>
+        <v>1024534468</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1014248976</v>
+        <v>1000272392</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,19 +1375,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Lina Andrea Peralta Navarro</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1020792634</v>
+        <v>1072719991</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2968000</v>
+        <v>2544000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1403,19 +1403,19 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1000272392</v>
+        <v>1097332216</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2968000</v>
+        <v>2544000</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1431,19 +1431,19 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>94446125</v>
+        <v>1129568417</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2968000</v>
+        <v>2544000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1459,19 +1459,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Supervisor 2</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1078180826</v>
+        <v>2222222</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t>Supervisor</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2544000</v>
+        <v>5000000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1480,26 +1480,26 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Angelica Morales Garcia</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1032416590</v>
+        <v>35379078</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t>Master</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2544000</v>
+        <v>4028000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1508,26 +1508,26 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1054681147</v>
+        <v>1012466465</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2544000</v>
+        <v>2968000</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1536,26 +1536,26 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grupo 3</t>
+          <t>Grupo 4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Supervisor 3</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3333333</v>
+        <v>1018432981</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Supervisor</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5000000</v>
+        <v>2968000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1571,19 +1571,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jimmy Alexander Daza Tarquino</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>80208472</v>
+        <v>1016039845</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>4028000</v>
+        <v>2968000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1599,19 +1599,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Adriana Milena Perez Betancourth</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>33819510</v>
+        <v>93138251</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Tecnico A</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>4028000</v>
+        <v>2968000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>80830605</v>
+        <v>1024593756</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1019131043</v>
+        <v>1016066574</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1014192228</v>
+        <v>1030578335</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1711,19 +1711,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1013630135</v>
+        <v>1073721158</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2968000</v>
+        <v>2544000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1739,19 +1739,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1014232367</v>
+        <v>1073234269</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2968000</v>
+        <v>2544000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1767,19 +1767,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>80912134</v>
+        <v>1054681147</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t>Tecnico B</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2968000</v>
+        <v>2544000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1795,19 +1795,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1024512643</v>
-      </c>
+          <t>AA01</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tecnico A</t>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2968000</v>
+        <v>1751000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1816,26 +1814,24 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Lina Andrea Peralta Navarro</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1072719991</v>
-      </c>
+          <t>AA02</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2544000</v>
+        <v>1751000</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1844,26 +1840,24 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>1097332216</v>
-      </c>
+          <t>AA03</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2544000</v>
+        <v>1751000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1872,26 +1866,24 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>1129568417</v>
-      </c>
+          <t>AA04</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tecnico B</t>
+          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2544000</v>
+        <v>1751000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1900,14 +1892,14 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grupo 4</t>
+          <t>Abordaje</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AA01</t>
+          <t>AA05</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -1933,7 +1925,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AA02</t>
+          <t>AA06</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -1959,7 +1951,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AA03</t>
+          <t>AA07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -1985,7 +1977,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AA04</t>
+          <t>AA08</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2011,7 +2003,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AA05</t>
+          <t>AA09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2037,7 +2029,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AA06</t>
+          <t>AA10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2063,7 +2055,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AA07</t>
+          <t>AA11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2089,7 +2081,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AA08</t>
+          <t>AA12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2115,7 +2107,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AA09</t>
+          <t>AA13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2141,7 +2133,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AA10</t>
+          <t>AA14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2167,7 +2159,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AA11</t>
+          <t>AA15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2193,7 +2185,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AA12</t>
+          <t>AA16</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2219,7 +2211,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AA13</t>
+          <t>AA17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2245,7 +2237,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AA14</t>
+          <t>AA18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2271,7 +2263,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AA15</t>
+          <t>AA19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2297,7 +2289,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AA16</t>
+          <t>AA20</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2323,7 +2315,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AA17</t>
+          <t>AA21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2349,7 +2341,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AA18</t>
+          <t>AA22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2375,7 +2367,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AA19</t>
+          <t>AA23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2401,7 +2393,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AA20</t>
+          <t>AA24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2427,7 +2419,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AA21</t>
+          <t>AA25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -2453,7 +2445,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AA22</t>
+          <t>AA26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2479,7 +2471,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AA23</t>
+          <t>AA27</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -2497,110 +2489,6 @@
         </is>
       </c>
       <c r="F76" t="inlineStr">
-        <is>
-          <t>Abordaje</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>AA24</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Abordaje</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>AA25</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Abordaje</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>AA26</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Abordaje</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>AA27</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Auxiliar de Abordaje y Atención al Público </t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>1751000</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Cablemovil</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
         <is>
           <t>Abordaje</t>
         </is>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Supervisor 1</t>
+          <t>Supervisor 3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1111111</v>
+        <v>3333333</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Elias Alberto Santamaria Olachica</t>
+          <t>Jorge Medina Espinosa</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80251217</v>
+        <v>80213057</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -507,11 +507,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1030592271</v>
+        <v>1020792634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1014232367</v>
+        <v>94446125</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1020792634</v>
+        <v>1014238905</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1024512643</v>
+        <v>1010044018</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1013614915</v>
+        <v>1018434197</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94446125</v>
+        <v>1030592271</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1019131043</v>
+        <v>1012406573</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,11 +703,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rhayza Morella Fagundez Real</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1127621316</v>
+        <v>1073687003</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1031142560</v>
+        <v>1097332216</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1078180826</v>
+        <v>1073234269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Supervisor 4</t>
+          <t>Supervisor 2</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>444444</v>
+        <v>2222222</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -815,11 +815,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Adriana Milena Perez Betancourth</t>
+          <t>Jesus Eduardo Urrego Cagua</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33819510</v>
+        <v>11204332</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>80912134</v>
+        <v>1018432981</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1013630135</v>
+        <v>1022971025</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>80830605</v>
+        <v>1019131043</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1022370155</v>
+        <v>93138251</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1014238905</v>
+        <v>80830605</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1012406573</v>
+        <v>1013630135</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1018434197</v>
+        <v>1016039845</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1039,11 +1039,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1032416590</v>
+        <v>1073721158</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1073687003</v>
+        <v>1054681147</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1030635367</v>
+        <v>1078180826</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Supervisor 3</t>
+          <t>Supervisor 1</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3333333</v>
+        <v>1111111</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Gloria Rocio Martinez</t>
+          <t>Elias Alberto Santamaria Olachica</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>39724105</v>
+        <v>80251217</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1010044018</v>
+        <v>1013614915</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1022971025</v>
+        <v>1012466465</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>93298014</v>
+        <v>1022370155</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1014248976</v>
+        <v>1000272392</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1014192228</v>
+        <v>80912134</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1024534468</v>
+        <v>93298014</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1000272392</v>
+        <v>1014232367</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,11 +1375,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lina Andrea Peralta Navarro</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1072719991</v>
+        <v>1129568417</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
+          <t>Lina Andrea Peralta Navarro</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1097332216</v>
+        <v>1072719991</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Rhayza Morella Fagundez Real</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1129568417</v>
+        <v>1127621316</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Supervisor 2</t>
+          <t>Supervisor 4</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2222222</v>
+        <v>444444</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Angelica Morales Garcia</t>
+          <t>Helmuth Andrey Baron Caceres</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>35379078</v>
+        <v>79822166</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1012466465</v>
+        <v>1014248976</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1543,11 +1543,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1018432981</v>
+        <v>1024593756</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1016039845</v>
+        <v>1024534468</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>93138251</v>
+        <v>1030578335</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1024593756</v>
+        <v>1014192228</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1016066574</v>
+        <v>1024512643</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1030578335</v>
+        <v>1016066574</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1711,11 +1711,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1073721158</v>
+        <v>1031142560</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1073234269</v>
+        <v>1032416590</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1767,11 +1767,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1054681147</v>
+        <v>1030635367</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Supervisor 3</t>
+          <t>Supervisor 4</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3333333</v>
+        <v>444444</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jorge Medina Espinosa</t>
+          <t>Gloria Rocio Martinez</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80213057</v>
+        <v>39724105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -507,11 +507,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1020792634</v>
+        <v>80912134</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>94446125</v>
+        <v>1018434197</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1014238905</v>
+        <v>1000272392</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1018434197</v>
+        <v>1016039845</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1030592271</v>
+        <v>1022971025</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1012406573</v>
+        <v>1016066574</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,11 +703,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1073687003</v>
+        <v>1073234269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1097332216</v>
+        <v>1031142560</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1073234269</v>
+        <v>1129568417</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1018432981</v>
+        <v>1022370155</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1022971025</v>
+        <v>1014248976</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1019131043</v>
+        <v>1018432981</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>93138251</v>
+        <v>94446125</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>80830605</v>
+        <v>1013614915</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1013630135</v>
+        <v>1012466465</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1016039845</v>
+        <v>1024593756</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1039,11 +1039,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1073721158</v>
+        <v>1073687003</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1054681147</v>
+        <v>1078180826</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1078180826</v>
+        <v>1030635367</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Elias Alberto Santamaria Olachica</t>
+          <t>Helmuth Andrey Baron Caceres</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>80251217</v>
+        <v>79822166</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1013614915</v>
+        <v>80830605</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1012466465</v>
+        <v>1014238905</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1022370155</v>
+        <v>1012406573</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1000272392</v>
+        <v>1024534468</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>80912134</v>
+        <v>93298014</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>93298014</v>
+        <v>1030592271</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1375,11 +1375,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1129568417</v>
+        <v>1073721158</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Lina Andrea Peralta Navarro</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1072719991</v>
+        <v>1097332216</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Supervisor 4</t>
+          <t>Supervisor 3</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>444444</v>
+        <v>3333333</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Helmuth Andrey Baron Caceres</t>
+          <t>Angelica Morales Garcia</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>79822166</v>
+        <v>35379078</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1014248976</v>
+        <v>93138251</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1543,11 +1543,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1024593756</v>
+        <v>1014192228</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1024534468</v>
+        <v>1019131043</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1030578335</v>
+        <v>1013630135</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1014192228</v>
+        <v>1020792634</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1016066574</v>
+        <v>1030578335</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1711,11 +1711,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Lina Andrea Peralta Navarro</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1031142560</v>
+        <v>1072719991</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1032416590</v>
+        <v>1054681147</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1767,11 +1767,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1030635367</v>
+        <v>1032416590</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Supervisor 4</t>
+          <t>Supervisor 2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>444444</v>
+        <v>2222222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Gloria Rocio Martinez</t>
+          <t>Jesus Eduardo Urrego Cagua</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39724105</v>
+        <v>11204332</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -507,11 +507,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80912134</v>
+        <v>80830605</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1018434197</v>
+        <v>1020792634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1000272392</v>
+        <v>1013630135</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1010044018</v>
+        <v>1012466465</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1016039845</v>
+        <v>80912134</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1022971025</v>
+        <v>1030578335</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1016066574</v>
+        <v>1014192228</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,11 +703,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Lina Andrea Peralta Navarro</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1073234269</v>
+        <v>1072719991</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1031142560</v>
+        <v>1129568417</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1129568417</v>
+        <v>1078180826</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Supervisor 2</t>
+          <t>Supervisor 3</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2222222</v>
+        <v>3333333</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -815,11 +815,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Angelica Morales Garcia</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11204332</v>
+        <v>35379078</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1022370155</v>
+        <v>1024593756</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1014248976</v>
+        <v>1016066574</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1018432981</v>
+        <v>1014248976</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>94446125</v>
+        <v>1014238905</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1013614915</v>
+        <v>1018432981</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1012466465</v>
+        <v>1016039845</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1024593756</v>
+        <v>1024534468</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1039,11 +1039,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1073687003</v>
+        <v>1031142560</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1078180826</v>
+        <v>1073721158</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1030635367</v>
+        <v>1097332216</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Supervisor 1</t>
+          <t>Supervisor 4</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1111111</v>
+        <v>444444</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Helmuth Andrey Baron Caceres</t>
+          <t>Jorge Medina Espinosa</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>79822166</v>
+        <v>80213057</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>80830605</v>
+        <v>1000272392</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1014238905</v>
+        <v>1014232367</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1012406573</v>
+        <v>93138251</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1024534468</v>
+        <v>93298014</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>93298014</v>
+        <v>1012406573</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1030592271</v>
+        <v>94446125</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1014232367</v>
+        <v>1022971025</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,11 +1375,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1073721158</v>
+        <v>1030635367</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1097332216</v>
+        <v>1073687003</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Supervisor 3</t>
+          <t>Supervisor 1</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3333333</v>
+        <v>1111111</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Angelica Morales Garcia</t>
+          <t>Gloria Rocio Martinez</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>35379078</v>
+        <v>39724105</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>93138251</v>
+        <v>1030592271</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1543,11 +1543,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1014192228</v>
+        <v>1019131043</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1019131043</v>
+        <v>1010044018</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1013630135</v>
+        <v>1024512643</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1020792634</v>
+        <v>1013614915</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1024512643</v>
+        <v>1018434197</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1030578335</v>
+        <v>1022370155</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1711,11 +1711,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Lina Andrea Peralta Navarro</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1072719991</v>
+        <v>1054681147</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1054681147</v>
+        <v>1073234269</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Supervisor 2</t>
+          <t>Supervisor 1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2222222</v>
+        <v>1111111</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -507,11 +507,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>80830605</v>
+        <v>1022370155</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1020792634</v>
+        <v>93298014</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1013630135</v>
+        <v>1020792634</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1012466465</v>
+        <v>1024593756</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>80912134</v>
+        <v>1030592271</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1030578335</v>
+        <v>1013630135</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1129568417</v>
+        <v>1054681147</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1078180826</v>
+        <v>1031142560</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -815,11 +815,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Angelica Morales Garcia</t>
+          <t>Helmuth Andrey Baron Caceres</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35379078</v>
+        <v>79822166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1024593756</v>
+        <v>1019131043</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1016066574</v>
+        <v>1000272392</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1014248976</v>
+        <v>1030578335</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1014238905</v>
+        <v>94446125</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1018432981</v>
+        <v>1014248976</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1016039845</v>
+        <v>80912134</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1024534468</v>
+        <v>1016039845</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1039,11 +1039,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1031142560</v>
+        <v>1073687003</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1097332216</v>
+        <v>1073234269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Supervisor 4</t>
+          <t>Supervisor 2</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>444444</v>
+        <v>2222222</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jorge Medina Espinosa</t>
+          <t>Angelica Morales Garcia</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>80213057</v>
+        <v>35379078</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1000272392</v>
+        <v>1024512643</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1014232367</v>
+        <v>1010044018</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>93138251</v>
+        <v>1022971025</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>93298014</v>
+        <v>1012466465</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1012406573</v>
+        <v>1018432981</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>94446125</v>
+        <v>1013614915</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1022971025</v>
+        <v>1014238905</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,11 +1375,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1030635367</v>
+        <v>1032416590</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Rhayza Morella Fagundez Real</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1073687003</v>
+        <v>1127621316</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rhayza Morella Fagundez Real</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1127621316</v>
+        <v>1097332216</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Supervisor 1</t>
+          <t>Supervisor 4</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1111111</v>
+        <v>444444</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gloria Rocio Martinez</t>
+          <t>Jorge Medina Espinosa</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>39724105</v>
+        <v>80213057</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1030592271</v>
+        <v>93138251</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1543,11 +1543,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1019131043</v>
+        <v>1016066574</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1010044018</v>
+        <v>1014232367</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1024512643</v>
+        <v>1012406573</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1013614915</v>
+        <v>80830605</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1022370155</v>
+        <v>1024534468</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1711,11 +1711,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1054681147</v>
+        <v>1078180826</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1073234269</v>
+        <v>1129568417</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1767,11 +1767,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1032416590</v>
+        <v>1030635367</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Supervisor 1</t>
+          <t>Supervisor 3</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1111111</v>
+        <v>3333333</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Helmuth Andrey Baron Caceres</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11204332</v>
+        <v>79822166</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -507,11 +507,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1022370155</v>
+        <v>1012466465</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>93298014</v>
+        <v>1022370155</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1020792634</v>
+        <v>93138251</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1024593756</v>
+        <v>1000272392</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1030592271</v>
+        <v>1018432981</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1013630135</v>
+        <v>1020792634</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1014192228</v>
+        <v>1014232367</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,11 +703,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lina Andrea Peralta Navarro</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1072719991</v>
+        <v>1129568417</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1054681147</v>
+        <v>1073687003</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1031142560</v>
+        <v>1054681147</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Supervisor 3</t>
+          <t>Supervisor 1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3333333</v>
+        <v>1111111</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -815,11 +815,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Helmuth Andrey Baron Caceres</t>
+          <t>Jimmy Alexander Daza Tarquino</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>79822166</v>
+        <v>80208472</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1019131043</v>
+        <v>1024593756</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1000272392</v>
+        <v>80912134</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1030578335</v>
+        <v>93298014</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>94446125</v>
+        <v>1010044018</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1014248976</v>
+        <v>1016066574</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>80912134</v>
+        <v>1024512643</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1016039845</v>
+        <v>1014192228</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1039,11 +1039,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1073687003</v>
+        <v>1073234269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Lina Andrea Peralta Navarro</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1073721158</v>
+        <v>1072719991</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1073234269</v>
+        <v>1030635367</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Supervisor 2</t>
+          <t>Supervisor 4</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2222222</v>
+        <v>444444</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Angelica Morales Garcia</t>
+          <t>Elias Alberto Santamaria Olachica</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>35379078</v>
+        <v>80251217</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1024512643</v>
+        <v>1018434197</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1010044018</v>
+        <v>1022971025</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1022971025</v>
+        <v>1030592271</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1012466465</v>
+        <v>80830605</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1018432981</v>
+        <v>1019131043</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1013614915</v>
+        <v>1014248976</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1014238905</v>
+        <v>1016039845</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,11 +1375,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1032416590</v>
+        <v>1097332216</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rhayza Morella Fagundez Real</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1127621316</v>
+        <v>1031142560</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1097332216</v>
+        <v>1073721158</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Supervisor 4</t>
+          <t>Supervisor 2</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>444444</v>
+        <v>2222222</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jorge Medina Espinosa</t>
+          <t>Jesus Eduardo Urrego Cagua</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>80213057</v>
+        <v>11204332</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>93138251</v>
+        <v>1024534468</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1543,11 +1543,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1016066574</v>
+        <v>1013614915</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1014232367</v>
+        <v>1030578335</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1012406573</v>
+        <v>94446125</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>80830605</v>
+        <v>1014238905</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1018434197</v>
+        <v>1013630135</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1024534468</v>
+        <v>1012406573</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1129568417</v>
+        <v>1032416590</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1767,11 +1767,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Rhayza Morella Fagundez Real</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1030635367</v>
+        <v>1127621316</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Helmuth Andrey Baron Caceres</t>
+          <t>Jimmy Alexander Daza Tarquino</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79822166</v>
+        <v>80208472</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -507,11 +507,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1012466465</v>
+        <v>1022370155</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1022370155</v>
+        <v>94446125</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93138251</v>
+        <v>1012466465</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1000272392</v>
+        <v>1019131043</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1018432981</v>
+        <v>1013614915</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1020792634</v>
+        <v>1024534468</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1014232367</v>
+        <v>1014238905</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,11 +703,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1129568417</v>
+        <v>1030635367</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1073687003</v>
+        <v>1097332216</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1054681147</v>
+        <v>1031142560</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -815,11 +815,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jimmy Alexander Daza Tarquino</t>
+          <t>Jorge Medina Espinosa</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>80208472</v>
+        <v>80213057</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1024593756</v>
+        <v>1014232367</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>80912134</v>
+        <v>1016066574</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>93298014</v>
+        <v>1014248976</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1010044018</v>
+        <v>93298014</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1016066574</v>
+        <v>1022971025</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1024512643</v>
+        <v>1018432981</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1014192228</v>
+        <v>1000272392</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1039,11 +1039,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Lina Andrea Peralta Navarro</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1073234269</v>
+        <v>1072719991</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lina Andrea Peralta Navarro</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1072719991</v>
+        <v>1032416590</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1030635367</v>
+        <v>1073234269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Supervisor 4</t>
+          <t>Supervisor 2</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>444444</v>
+        <v>2222222</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Elias Alberto Santamaria Olachica</t>
+          <t>Adriana Milena Perez Betancourth</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>80251217</v>
+        <v>33819510</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1018434197</v>
+        <v>80912134</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1022971025</v>
+        <v>1013630135</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1030592271</v>
+        <v>1024593756</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>80830605</v>
+        <v>1024512643</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1019131043</v>
+        <v>93138251</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1014248976</v>
+        <v>1010044018</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1016039845</v>
+        <v>1030592271</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,11 +1375,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1097332216</v>
+        <v>1129568417</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1031142560</v>
+        <v>1073721158</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1073721158</v>
+        <v>1073687003</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Supervisor 2</t>
+          <t>Supervisor 4</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2222222</v>
+        <v>444444</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Elias Alberto Santamaria Olachica</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>11204332</v>
+        <v>80251217</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1024534468</v>
+        <v>80830605</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1543,11 +1543,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1013614915</v>
+        <v>1020792634</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1030578335</v>
+        <v>1012406573</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>94446125</v>
+        <v>1018434197</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1014238905</v>
+        <v>1016039845</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1013630135</v>
+        <v>1030578335</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1012406573</v>
+        <v>1014192228</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1032416590</v>
+        <v>1054681147</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Supervisor 3</t>
+          <t>Supervisor 2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3333333</v>
+        <v>2222222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jimmy Alexander Daza Tarquino</t>
+          <t>Adriana Milena Perez Betancourth</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80208472</v>
+        <v>33819510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -507,11 +507,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1022370155</v>
+        <v>93298014</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>94446125</v>
+        <v>1020792634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1012466465</v>
+        <v>1018434197</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1019131043</v>
+        <v>1016039845</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1013614915</v>
+        <v>1014232367</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1024534468</v>
+        <v>80912134</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1014238905</v>
+        <v>1012406573</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,11 +703,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Rhayza Morella Fagundez Real</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1030635367</v>
+        <v>1127621316</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1097332216</v>
+        <v>1073721158</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1031142560</v>
+        <v>1032416590</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Supervisor 1</t>
+          <t>Supervisor 4</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1111111</v>
+        <v>444444</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1014232367</v>
+        <v>1019131043</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1016066574</v>
+        <v>1030592271</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1014248976</v>
+        <v>1024593756</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>93298014</v>
+        <v>1016066574</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1022971025</v>
+        <v>1010044018</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1018432981</v>
+        <v>1022971025</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1000272392</v>
+        <v>1030578335</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1032416590</v>
+        <v>1097332216</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1073234269</v>
+        <v>1030635367</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1123,11 +1123,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Supervisor 2</t>
+          <t>Supervisor 3</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2222222</v>
+        <v>3333333</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Adriana Milena Perez Betancourth</t>
+          <t>Gloria Rocio Martinez</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>33819510</v>
+        <v>39724105</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>80912134</v>
+        <v>1014238905</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1013630135</v>
+        <v>80830605</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1024593756</v>
+        <v>1014192228</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1024512643</v>
+        <v>1013614915</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>93138251</v>
+        <v>1000272392</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1010044018</v>
+        <v>1018432981</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1030592271</v>
+        <v>1024534468</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,11 +1375,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1129568417</v>
+        <v>1078180826</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1073721158</v>
+        <v>1129568417</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1073687003</v>
+        <v>1073234269</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Supervisor 4</t>
+          <t>Supervisor 1</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>444444</v>
+        <v>1111111</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Elias Alberto Santamaria Olachica</t>
+          <t>Jesus Eduardo Urrego Cagua</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>80251217</v>
+        <v>11204332</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>80830605</v>
+        <v>1022370155</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1543,11 +1543,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1020792634</v>
+        <v>1014248976</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1012406573</v>
+        <v>1024512643</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1018434197</v>
+        <v>1013630135</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1016039845</v>
+        <v>93138251</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1030578335</v>
+        <v>1012466465</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1014192228</v>
+        <v>94446125</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1711,11 +1711,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1078180826</v>
+        <v>1054681147</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1054681147</v>
+        <v>1073687003</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1767,11 +1767,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Rhayza Morella Fagundez Real</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1127621316</v>
+        <v>1031142560</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Supervisor 2</t>
+          <t>Supervisor 1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2222222</v>
+        <v>1111111</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Adriana Milena Perez Betancourth</t>
+          <t>Jesus Eduardo Urrego Cagua</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33819510</v>
+        <v>11204332</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -507,11 +507,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>93298014</v>
+        <v>1020792634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1020792634</v>
+        <v>1012406573</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1018434197</v>
+        <v>1000272392</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1016039845</v>
+        <v>1016066574</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1014232367</v>
+        <v>1022370155</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80912134</v>
+        <v>1016039845</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1012406573</v>
+        <v>1010044018</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,11 +703,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rhayza Morella Fagundez Real</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1127621316</v>
+        <v>1031142560</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1073721158</v>
+        <v>1129568417</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -815,11 +815,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Jorge Medina Espinosa</t>
+          <t>Helmuth Andrey Baron Caceres</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>80213057</v>
+        <v>79822166</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1019131043</v>
+        <v>1013614915</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1030592271</v>
+        <v>1024593756</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1024593756</v>
+        <v>93298014</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1016066574</v>
+        <v>1030578335</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1010044018</v>
+        <v>1018434197</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1022971025</v>
+        <v>94446125</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1030578335</v>
+        <v>1024534468</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1039,11 +1039,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lina Andrea Peralta Navarro</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1072719991</v>
+        <v>1073687003</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1097332216</v>
+        <v>1073234269</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1030635367</v>
+        <v>1054681147</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Gloria Rocio Martinez</t>
+          <t>Adriana Milena Perez Betancourth</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>39724105</v>
+        <v>33819510</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1014238905</v>
+        <v>80912134</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>80830605</v>
+        <v>1018432981</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1014192228</v>
+        <v>80830605</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1013614915</v>
+        <v>1014232367</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1000272392</v>
+        <v>1030592271</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1018432981</v>
+        <v>1014248976</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1024534468</v>
+        <v>1012466465</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,11 +1375,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Lina Andrea Peralta Navarro</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1078180826</v>
+        <v>1072719991</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1129568417</v>
+        <v>1030635367</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Rhayza Morella Fagundez Real</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1073234269</v>
+        <v>1127621316</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Supervisor 1</t>
+          <t>Supervisor 2</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1111111</v>
+        <v>2222222</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Angelica Morales Garcia</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>11204332</v>
+        <v>35379078</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1022370155</v>
+        <v>1014192228</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1543,11 +1543,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1014248976</v>
+        <v>1022971025</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1013630135</v>
+        <v>1014238905</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>93138251</v>
+        <v>1019131043</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1012466465</v>
+        <v>1013630135</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>94446125</v>
+        <v>93138251</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1711,11 +1711,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1054681147</v>
+        <v>1097332216</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1073687003</v>
+        <v>1078180826</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1767,11 +1767,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1031142560</v>
+        <v>1073721158</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Supervisor 1</t>
+          <t>Supervisor 2</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1111111</v>
+        <v>2222222</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -479,11 +479,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Jorge Medina Espinosa</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11204332</v>
+        <v>80213057</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -507,11 +507,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Wendy Carolina Quintero Alvarado</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1020792634</v>
+        <v>93298014</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1012406573</v>
+        <v>1022971025</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1000272392</v>
+        <v>1012466465</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1016066574</v>
+        <v>1024512643</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1022370155</v>
+        <v>1014232367</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1016039845</v>
+        <v>1014192228</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1010044018</v>
+        <v>80830605</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1129568417</v>
+        <v>1073234269</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1032416590</v>
+        <v>1078180826</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -815,11 +815,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Helmuth Andrey Baron Caceres</t>
+          <t>Adriana Milena Perez Betancourth</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>79822166</v>
+        <v>33819510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1013614915</v>
+        <v>80912134</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -871,11 +871,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Diana Aldana Gordillo</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1024593756</v>
+        <v>1018432981</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>93298014</v>
+        <v>1016039845</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1030578335</v>
+        <v>1010044018</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1018434197</v>
+        <v>1016066574</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>94446125</v>
+        <v>1012406573</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1024534468</v>
+        <v>1024593756</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1073234269</v>
+        <v>1129568417</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1054681147</v>
+        <v>1030635367</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Adriana Milena Perez Betancourth</t>
+          <t>Gloria Rocio Martinez</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>33819510</v>
+        <v>39724105</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>80912134</v>
+        <v>1013630135</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Diana Aldana Gordillo</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1018432981</v>
+        <v>1030578335</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>80830605</v>
+        <v>1030592271</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1014232367</v>
+        <v>1018434197</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1030592271</v>
+        <v>1000272392</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1014248976</v>
+        <v>1019131043</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1012466465</v>
+        <v>1014248976</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1030635367</v>
+        <v>1073721158</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Rhayza Morella Fagundez Real</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1127621316</v>
+        <v>1032416590</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Supervisor 2</t>
+          <t>Supervisor 1</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2222222</v>
+        <v>1111111</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Angelica Morales Garcia</t>
+          <t>Jesus Eduardo Urrego Cagua</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>35379078</v>
+        <v>11204332</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1014192228</v>
+        <v>93138251</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1543,11 +1543,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1022971025</v>
+        <v>1013614915</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1024512643</v>
+        <v>1014238905</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1014238905</v>
+        <v>1022370155</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1627,11 +1627,11 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Wendy Carolina Quintero Alvarado</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1019131043</v>
+        <v>1020792634</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1013630135</v>
+        <v>94446125</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>93138251</v>
+        <v>1024534468</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1078180826</v>
+        <v>1054681147</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1767,11 +1767,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Rhayza Morella Fagundez Real</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1073721158</v>
+        <v>1127621316</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/empleados_grupos.xlsx
+++ b/empleados_grupos.xlsx
@@ -451,11 +451,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Supervisor 2</t>
+          <t>Supervisor 4</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2222222</v>
+        <v>444444</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -507,11 +507,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Jhon Fredy Torres Rubio</t>
+          <t>Katherine Mosquera Torres</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>93298014</v>
+        <v>1024593756</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -535,11 +535,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lyda Astrid Recio Duarte</t>
+          <t>Alejandro AcuÃ±a Cortes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1022971025</v>
+        <v>1016066574</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -563,11 +563,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alis Yuranni Garcia Ospina</t>
+          <t>Ginna Daniela Amezquita Gutierrez</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1012466465</v>
+        <v>1018434197</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -591,11 +591,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Diego Soto Hernandez</t>
+          <t>Christian Felipe Martinez Camargo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1024512643</v>
+        <v>1013614915</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -619,11 +619,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Francisco Javier Plazas Gonzalez</t>
+          <t>Jennifer Lizcano Correa</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1014232367</v>
+        <v>1000272392</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -647,11 +647,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Luis Enrique Gutierrez Romero</t>
+          <t>Luis Fernando Rey BriceÃ±o</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1014192228</v>
+        <v>1019131043</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -675,11 +675,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Jose Giovanny Trujillo Florez</t>
+          <t>Alis Yuranni Garcia Ospina</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>80830605</v>
+        <v>1012466465</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -703,11 +703,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Millie Johanna Carrillo Prieto</t>
+          <t>Julian David Porras Sanchez</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1031142560</v>
+        <v>1054681147</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -731,11 +731,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Michael Rolf Corredor FandiÃ±o</t>
+          <t>Yerly Johana Sanchez Velasco</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1073234269</v>
+        <v>1097332216</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -759,11 +759,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Jhon Fredys Moreno Maturana</t>
+          <t>Carol Chayanne Guzman Rojas</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1078180826</v>
+        <v>1073687003</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -787,11 +787,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Supervisor 4</t>
+          <t>Supervisor 1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>444444</v>
+        <v>1111111</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -815,11 +815,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Adriana Milena Perez Betancourth</t>
+          <t>Jimmy Alexander Daza Tarquino</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33819510</v>
+        <v>80208472</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -843,11 +843,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Carlos Arturo Forero Vega</t>
+          <t>Johan Steeven Corredor Dominguez</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>80912134</v>
+        <v>1010044018</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -899,11 +899,11 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Antonio Jose Navarrete Calderon</t>
+          <t>Carlos Arturo Forero Vega</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1016039845</v>
+        <v>80912134</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -927,11 +927,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Johan Steeven Corredor Dominguez</t>
+          <t>Francisco Javier Plazas Gonzalez</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1010044018</v>
+        <v>1014232367</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -955,11 +955,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alejandro AcuÃ±a Cortes</t>
+          <t>Viviana Andrea Chavez Enciso</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1016066574</v>
+        <v>1014238905</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -983,11 +983,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mayerly Pardo Torres</t>
+          <t>Antonio Jose Navarrete Calderon</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1012406573</v>
+        <v>1016039845</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1011,11 +1011,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Katherine Mosquera Torres</t>
+          <t>Cristineidy Roa Calderon</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1024593756</v>
+        <v>1030592271</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1039,11 +1039,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Carol Chayanne Guzman Rojas</t>
+          <t>Yuli Alejandra Casas Jerez</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1073687003</v>
+        <v>1032416590</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1067,11 +1067,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Andres Guillermo Castro Coronado</t>
+          <t>Cesar Ivan CastaÃ±eda Baquero</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1129568417</v>
+        <v>1030635367</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1095,11 +1095,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cesar Ivan CastaÃ±eda Baquero</t>
+          <t>Rhayza Morella Fagundez Real</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1030635367</v>
+        <v>1127621316</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1151,11 +1151,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Gloria Rocio Martinez</t>
+          <t>Angelica Morales Garcia</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>39724105</v>
+        <v>35379078</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1179,11 +1179,11 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Natalia Ospina Serrato</t>
+          <t>Richard Stiven Guevara Patarroyo</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1013630135</v>
+        <v>1022370155</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1207,11 +1207,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
+          <t>Luis Enrique Gutierrez Romero</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1030578335</v>
+        <v>1014192228</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1235,11 +1235,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cristineidy Roa Calderon</t>
+          <t>Jose Giovanny Trujillo Florez</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1030592271</v>
+        <v>80830605</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1263,11 +1263,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Ginna Daniela Amezquita Gutierrez</t>
+          <t>Natalia Ospina Serrato</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1018434197</v>
+        <v>1013630135</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1291,11 +1291,11 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jennifer Lizcano Correa</t>
+          <t>Diego Soto Hernandez</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1000272392</v>
+        <v>1024512643</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1319,11 +1319,11 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Luis Fernando Rey BriceÃ±o</t>
+          <t>Carlos Alberto Vega Ramirez</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1019131043</v>
+        <v>94446125</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1347,11 +1347,11 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Karen Dayana Parra Borja</t>
+          <t>Mayerly Esperanza Riscanevo UrueÃ±a</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1014248976</v>
+        <v>1030578335</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1375,11 +1375,11 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lina Andrea Peralta Navarro</t>
+          <t>Andres Guillermo Castro Coronado</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1072719991</v>
+        <v>1129568417</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1403,11 +1403,11 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Miguel Angel Palacio Rodriguez</t>
+          <t>Millie Johanna Carrillo Prieto</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1073721158</v>
+        <v>1031142560</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1431,11 +1431,11 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Yuli Alejandra Casas Jerez</t>
+          <t>Miguel Angel Palacio Rodriguez</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1032416590</v>
+        <v>1073721158</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1459,11 +1459,11 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Supervisor 1</t>
+          <t>Supervisor 2</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1111111</v>
+        <v>2222222</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1487,11 +1487,11 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Jesus Eduardo Urrego Cagua</t>
+          <t>Helmuth Andrey Baron Caceres</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>11204332</v>
+        <v>79822166</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1515,11 +1515,11 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Excehomo Jose Morales Bernal</t>
+          <t>Solbey Yorely Alza Correa</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>93138251</v>
+        <v>1024534468</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1543,11 +1543,11 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Christian Felipe Martinez Camargo</t>
+          <t>Lyda Astrid Recio Duarte</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1013614915</v>
+        <v>1022971025</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1571,11 +1571,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Viviana Andrea Chavez Enciso</t>
+          <t>Excehomo Jose Morales Bernal</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1014238905</v>
+        <v>93138251</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1599,11 +1599,11 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Richard Stiven Guevara Patarroyo</t>
+          <t>Mayerly Pardo Torres</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1022370155</v>
+        <v>1012406573</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1655,11 +1655,11 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Carlos Alberto Vega Ramirez</t>
+          <t>Jhon Fredy Torres Rubio</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>94446125</v>
+        <v>93298014</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1683,11 +1683,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Solbey Yorely Alza Correa</t>
+          <t>Karen Dayana Parra Borja</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1024534468</v>
+        <v>1014248976</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1711,11 +1711,11 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Yerly Johana Sanchez Velasco</t>
+          <t>Michael Rolf Corredor FandiÃ±o</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1097332216</v>
+        <v>1073234269</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1739,11 +1739,11 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Julian David Porras Sanchez</t>
+          <t>Jhon Fredys Moreno Maturana</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1054681147</v>
+        <v>1078180826</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1767,11 +1767,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Rhayza Morella Fagundez Real</t>
+          <t>Lina Andrea Peralta Navarro</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1127621316</v>
+        <v>1072719991</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
